--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.962429422585638</v>
+        <v>1.618894781170166</v>
       </c>
       <c r="D2" t="n">
-        <v>26.80018656651479</v>
+        <v>4.355030317058654</v>
       </c>
       <c r="E2" t="n">
-        <v>6.669438322241001</v>
+        <v>1.083783727364163</v>
       </c>
       <c r="F2" t="n">
-        <v>11.55967193376719</v>
+        <v>1.878446689237168</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.00302112335515</v>
+        <v>1.787990932545212</v>
       </c>
       <c r="D3" t="n">
-        <v>9.433981132056603</v>
+        <v>1.533021933959198</v>
       </c>
       <c r="E3" t="n">
-        <v>6.669438322241001</v>
+        <v>1.083783727364163</v>
       </c>
       <c r="F3" t="n">
-        <v>11.55967193376719</v>
+        <v>1.878446689237168</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.932957264424541</v>
+        <v>1.126605555468988</v>
       </c>
       <c r="D4" t="n">
-        <v>5.113967441583108</v>
+        <v>0.831019709257255</v>
       </c>
       <c r="E4" t="n">
-        <v>6.669438322241001</v>
+        <v>1.083783727364163</v>
       </c>
       <c r="F4" t="n">
-        <v>11.55967193376719</v>
+        <v>1.878446689237168</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.93906228851538</v>
+        <v>1.777597621883749</v>
       </c>
       <c r="D5" t="n">
-        <v>26.00480724789169</v>
+        <v>4.225781177782399</v>
       </c>
       <c r="E5" t="n">
-        <v>6.669438322241001</v>
+        <v>1.083783727364163</v>
       </c>
       <c r="F5" t="n">
-        <v>11.55967193376719</v>
+        <v>1.878446689237168</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.577675234721812</v>
+        <v>0.4188722256422945</v>
       </c>
       <c r="D6" t="n">
-        <v>37.97696670351649</v>
+        <v>6.17125708932143</v>
       </c>
       <c r="E6" t="n">
-        <v>6.669438322241001</v>
+        <v>1.083783727364163</v>
       </c>
       <c r="F6" t="n">
-        <v>11.55967193376719</v>
+        <v>1.878446689237168</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.35442356128845</v>
+        <v>3.957593828709374</v>
       </c>
       <c r="D7" t="n">
-        <v>30.14770267848538</v>
+        <v>4.899001685253874</v>
       </c>
       <c r="E7" t="n">
-        <v>6.669438322241001</v>
+        <v>1.083783727364163</v>
       </c>
       <c r="F7" t="n">
-        <v>11.55967193376719</v>
+        <v>1.878446689237168</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
